--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9827,0.0028,0.0012,0.0050</t>
-  </si>
-  <si>
-    <t>0.0088,0.0004,0.0005,0.9958</t>
-  </si>
-  <si>
-    <t>0.8201,0.0024,0.0014,0.2801</t>
-  </si>
-  <si>
-    <t>0.0973,0.0006,0.0003,0.9803</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9883,0.0108,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9947,0.0081,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0014,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0018,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9781,0.0015,0.0161,0.0002</t>
-  </si>
-  <si>
-    <t>0.0380,0.0079,0.9684,0.0023</t>
-  </si>
-  <si>
-    <t>0.6427,0.0058,0.5844,0.0003</t>
-  </si>
-  <si>
-    <t>0.0202,0.0136,0.9714,0.0086</t>
-  </si>
-  <si>
-    <t>0.8185,0.0041,0.1723,0.0091</t>
-  </si>
-  <si>
-    <t>0.0109,0.9818,0.0087,0.0007</t>
-  </si>
-  <si>
-    <t>0.0020,0.9949,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.0265,0.9563,0.0447,0.0033</t>
-  </si>
-  <si>
-    <t>0.0035,0.9913,0.0044,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.9973,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9310,0.0016,0.0944,0.0009</t>
-  </si>
-  <si>
-    <t>0.2635,0.0094,0.7421,0.0104</t>
-  </si>
-  <si>
-    <t>0.0035,0.0005,0.9966,0.0003</t>
-  </si>
-  <si>
-    <t>0.0705,0.0120,0.9170,0.0059</t>
-  </si>
-  <si>
-    <t>0.1199,0.0029,0.9487,0.0007</t>
-  </si>
-  <si>
-    <t>0.1277,0.0039,0.9014,0.0112</t>
-  </si>
-  <si>
-    <t>0.0077,0.0009,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.7203,0.4067,0.0046,0.0021</t>
-  </si>
-  <si>
-    <t>0.5885,0.4478,0.0469,0.0016</t>
-  </si>
-  <si>
-    <t>0.0012,0.0482,0.9976,0.0004</t>
-  </si>
-  <si>
-    <t>0.0177,0.9685,0.0163,0.0005</t>
-  </si>
-  <si>
-    <t>0.9489,0.0459,0.0071,0.0062</t>
-  </si>
-  <si>
-    <t>0.9286,0.0343,0.0260,0.0073</t>
-  </si>
-  <si>
-    <t>0.6018,0.6119,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0068,0.9847,0.0580,0.0012</t>
-  </si>
-  <si>
-    <t>0.0713,0.0346,0.8157,0.0142</t>
-  </si>
-  <si>
-    <t>0.3050,0.0007,0.5506,0.0075</t>
-  </si>
-  <si>
-    <t>0.3874,0.0029,0.8415,0.0002</t>
-  </si>
-  <si>
-    <t>0.5219,0.0019,0.5880,0.0037</t>
-  </si>
-  <si>
-    <t>0.0061,0.2087,0.9919,0.0003</t>
-  </si>
-  <si>
-    <t>0.0152,0.9676,0.0066,0.0014</t>
-  </si>
-  <si>
-    <t>0.0264,0.1447,0.9047,0.0059</t>
-  </si>
-  <si>
-    <t>0.0042,0.8419,0.0023,0.7985</t>
-  </si>
-  <si>
-    <t>0.0037,0.9900,0.0037,0.0019</t>
-  </si>
-  <si>
-    <t>0.0293,0.9618,0.0099,0.0004</t>
-  </si>
-  <si>
-    <t>0.0210,0.9677,0.0548,0.0017</t>
-  </si>
-  <si>
-    <t>0.0005,0.0022,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.0037,0.4808,0.9713,0.0010</t>
-  </si>
-  <si>
-    <t>0.0245,0.0017,0.9842,0.0007</t>
-  </si>
-  <si>
-    <t>0.0094,0.0023,0.9926,0.0007</t>
-  </si>
-  <si>
-    <t>0.0618,0.0080,0.9509,0.0006</t>
-  </si>
-  <si>
-    <t>0.0086,0.1363,0.9540,0.0002</t>
-  </si>
-  <si>
-    <t>0.9593,0.0657,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9893,0.0056,0.0015,0.0017</t>
-  </si>
-  <si>
-    <t>0.9914,0.0025,0.0035,0.0004</t>
-  </si>
-  <si>
-    <t>0.0077,0.4554,0.9830,0.0085</t>
-  </si>
-  <si>
-    <t>0.9913,0.0058,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9980,0.0014,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9828,0.0266,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9613,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.1712,0.9796,0.0020</t>
-  </si>
-  <si>
-    <t>0.0024,0.0022,0.9942,0.0015</t>
-  </si>
-  <si>
-    <t>0.0010,0.9470,0.9781,0.0002</t>
-  </si>
-  <si>
-    <t>0.0031,0.0034,0.9960,0.0005</t>
-  </si>
-  <si>
-    <t>0.0260,0.9701,0.0156,0.0001</t>
-  </si>
-  <si>
-    <t>0.0138,0.9868,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.2866,0.0024,0.8758,0.0011</t>
-  </si>
-  <si>
-    <t>0.1147,0.4930,0.6937,0.0124</t>
-  </si>
-  <si>
-    <t>0.0020,0.0732,0.9947,0.0016</t>
-  </si>
-  <si>
-    <t>0.0027,0.9264,0.8309,0.0005</t>
-  </si>
-  <si>
-    <t>0.0081,0.8727,0.6118,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9961,0.0086,0.0010</t>
-  </si>
-  <si>
-    <t>0.0031,0.9682,0.2374,0.0114</t>
-  </si>
-  <si>
-    <t>0.0050,0.0002,0.0008,0.9973</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0104,0.0000,0.0000,0.9987</t>
-  </si>
-  <si>
-    <t>0.0336,0.0028,0.0003,0.9876</t>
-  </si>
-  <si>
-    <t>0.0177,0.0023,0.0007,0.9920</t>
-  </si>
-  <si>
-    <t>0.0007,0.0030,0.0002,0.9989</t>
-  </si>
-  <si>
-    <t>0.0008,0.9905,0.7827,0.0001</t>
-  </si>
-  <si>
-    <t>0.0076,0.5878,0.9800,0.0005</t>
-  </si>
-  <si>
-    <t>0.0118,0.1398,0.9196,0.0056</t>
-  </si>
-  <si>
-    <t>0.0171,0.9084,0.6777,0.0034</t>
-  </si>
-  <si>
-    <t>0.0085,0.8775,0.8523,0.0016</t>
-  </si>
-  <si>
-    <t>0.0052,0.8922,0.5610,0.0006</t>
-  </si>
-  <si>
-    <t>0.9978,0.0012,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9897,0.0165,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9954,0.0038,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0042,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0018,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9969,0.0013,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9939,0.0074,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0010,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9962,0.0014,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.0021,0.0014,0.9980,0.0005</t>
-  </si>
-  <si>
-    <t>0.0201,0.0106,0.9851,0.0004</t>
-  </si>
-  <si>
-    <t>0.9038,0.0054,0.0486,0.0148</t>
-  </si>
-  <si>
-    <t>0.0140,0.0022,0.9919,0.0003</t>
-  </si>
-  <si>
-    <t>0.0065,0.9888,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.0344,0.9656,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.0057,0.9923,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.1153,0.8923,0.0160,0.0011</t>
-  </si>
-  <si>
-    <t>0.0084,0.9882,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.9973,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.1443,0.8934,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.3719,0.4065,0.3113,0.0643</t>
-  </si>
-  <si>
-    <t>0.3052,0.0032,0.8089,0.0013</t>
-  </si>
-  <si>
-    <t>0.8844,0.0102,0.1111,0.0036</t>
-  </si>
-  <si>
-    <t>0.2754,0.0900,0.6850,0.0048</t>
-  </si>
-  <si>
-    <t>0.0454,0.1386,0.0532,0.9114</t>
-  </si>
-  <si>
-    <t>0.0294,0.9683,0.0179,0.0005</t>
-  </si>
-  <si>
-    <t>0.0148,0.9769,0.0320,0.0016</t>
-  </si>
-  <si>
-    <t>0.0052,0.9874,0.0125,0.0034</t>
-  </si>
-  <si>
-    <t>0.0021,0.9895,0.1285,0.0040</t>
-  </si>
-  <si>
-    <t>0.0313,0.9711,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.3531,0.7239,0.0178,0.0021</t>
-  </si>
-  <si>
-    <t>0.9019,0.1615,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9940,0.0007,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.9958,0.0002,0.0001,0.0029</t>
-  </si>
-  <si>
-    <t>0.9970,0.0011,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9964,0.0005,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0005,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.8927,0.9796,0.0004</t>
-  </si>
-  <si>
-    <t>0.0027,0.3656,0.9623,0.0005</t>
-  </si>
-  <si>
-    <t>0.0072,0.0536,0.9711,0.0017</t>
-  </si>
-  <si>
-    <t>0.0022,0.0207,0.9918,0.0009</t>
-  </si>
-  <si>
-    <t>0.9843,0.0033,0.0033,0.0014</t>
-  </si>
-  <si>
-    <t>0.9210,0.0052,0.0280,0.0143</t>
-  </si>
-  <si>
-    <t>0.4959,0.0003,0.7800,0.0003</t>
-  </si>
-  <si>
-    <t>0.2743,0.0362,0.7514,0.0092</t>
-  </si>
-  <si>
-    <t>0.0333,0.0005,0.0002,0.9926</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0081,0.0009,0.0002,0.9973</t>
-  </si>
-  <si>
-    <t>0.0045,0.0002,0.0000,0.9989</t>
-  </si>
-  <si>
-    <t>0.0030,0.8632,0.9626,0.0006</t>
-  </si>
-  <si>
-    <t>0.9930,0.0020,0.0007,0.0018</t>
-  </si>
-  <si>
-    <t>0.0327,0.9480,0.0038,0.0272</t>
-  </si>
-  <si>
-    <t>0.9966,0.0003,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.7838,0.2678,0.0031,0.0022</t>
-  </si>
-  <si>
-    <t>0.9840,0.0078,0.0034,0.0020</t>
-  </si>
-  <si>
-    <t>0.8237,0.0195,0.0055,0.2051</t>
-  </si>
-  <si>
-    <t>0.9979,0.0006,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.0047,0.3674,0.9422,0.0366</t>
-  </si>
-  <si>
-    <t>0.8605,0.0019,0.0033,0.2096</t>
-  </si>
-  <si>
-    <t>0.9663,0.0106,0.0075,0.0110</t>
-  </si>
-  <si>
-    <t>0.0842,0.8779,0.0554,0.0164</t>
-  </si>
-  <si>
-    <t>0.9716,0.0193,0.0027,0.0021</t>
-  </si>
-  <si>
-    <t>0.9654,0.0133,0.0103,0.0028</t>
-  </si>
-  <si>
-    <t>0.3345,0.5842,0.0926,0.0245</t>
-  </si>
-  <si>
-    <t>0.9383,0.0117,0.0511,0.0011</t>
-  </si>
-  <si>
-    <t>0.9588,0.0156,0.0174,0.0028</t>
-  </si>
-  <si>
-    <t>0.9944,0.0022,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9976,0.0003,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9977,0.0008,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9932,0.0021,0.0008,0.0016</t>
-  </si>
-  <si>
-    <t>0.9917,0.0054,0.0014,0.0010</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9946,0.0015,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9086,0.1516,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9039,0.1370,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.6926,0.3751,0.0121,0.0011</t>
-  </si>
-  <si>
-    <t>0.0951,0.1339,0.8845,0.0174</t>
-  </si>
-  <si>
-    <t>0.9857,0.0227,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9909,0.0068,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9964,0.0020,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9935,0.0045,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0043,0.0163,0.9958,0.0004</t>
-  </si>
-  <si>
-    <t>0.9874,0.0185,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0109,0.0047,0.9877,0.0014</t>
-  </si>
-  <si>
-    <t>0.0126,0.0633,0.9571,0.0079</t>
-  </si>
-  <si>
-    <t>0.0550,0.0009,0.9793,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.0314,0.9952,0.0006</t>
-  </si>
-  <si>
-    <t>0.0038,0.0127,0.9886,0.0036</t>
-  </si>
-  <si>
-    <t>0.0600,0.0011,0.9688,0.0004</t>
-  </si>
-  <si>
-    <t>0.0038,0.0243,0.9882,0.0049</t>
-  </si>
-  <si>
-    <t>0.1140,0.0101,0.8955,0.0058</t>
-  </si>
-  <si>
-    <t>0.0280,0.0167,0.9602,0.0059</t>
-  </si>
-  <si>
-    <t>0.0590,0.0530,0.9031,0.0077</t>
-  </si>
-  <si>
-    <t>0.2004,0.0512,0.7597,0.0013</t>
-  </si>
-  <si>
-    <t>0.0647,0.2043,0.7448,0.0017</t>
-  </si>
-  <si>
-    <t>0.2855,0.0019,0.8501,0.0006</t>
-  </si>
-  <si>
-    <t>0.5241,0.0488,0.4470,0.0577</t>
-  </si>
-  <si>
-    <t>0.1532,0.0070,0.9113,0.0006</t>
-  </si>
-  <si>
-    <t>0.6610,0.5642,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0403,0.9678,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9871,0.0229,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9690,0.0419,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.3894,0.6697,0.0040,0.0035</t>
-  </si>
-  <si>
-    <t>0.5815,0.4382,0.0216,0.0020</t>
-  </si>
-  <si>
-    <t>0.9825,0.0005,0.0134,0.0002</t>
-  </si>
-  <si>
-    <t>0.9489,0.0038,0.0077,0.0159</t>
-  </si>
-  <si>
-    <t>0.7608,0.0044,0.3788,0.0016</t>
-  </si>
-  <si>
-    <t>0.2772,0.0056,0.7585,0.0233</t>
-  </si>
-  <si>
-    <t>0.0179,0.0099,0.9683,0.0224</t>
-  </si>
-  <si>
-    <t>0.0151,0.0453,0.9567,0.0075</t>
-  </si>
-  <si>
-    <t>0.0787,0.0109,0.9456,0.0013</t>
-  </si>
-  <si>
-    <t>0.1389,0.0175,0.8911,0.0023</t>
-  </si>
-  <si>
-    <t>0.1124,0.0608,0.8364,0.0033</t>
-  </si>
-  <si>
-    <t>0.9948,0.0028,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9961,0.0033,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9931,0.0071,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9952,0.0060,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0013,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9984,0.0010,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0013,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9978,0.0012,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0133,0.0076,0.9869,0.0021</t>
-  </si>
-  <si>
-    <t>0.0291,0.5641,0.7979,0.0042</t>
-  </si>
-  <si>
-    <t>0.9835,0.0049,0.0039,0.0028</t>
-  </si>
-  <si>
-    <t>0.0264,0.0062,0.9799,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.0029,0.9837,0.0096</t>
-  </si>
-  <si>
-    <t>0.0120,0.2083,0.9507,0.0019</t>
-  </si>
-  <si>
-    <t>0.0144,0.0010,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0346,0.0100,0.9590,0.0056</t>
-  </si>
-  <si>
-    <t>0.0006,0.0010,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0267,0.0073,0.9594,0.0038</t>
-  </si>
-  <si>
-    <t>0.0153,0.0113,0.9798,0.0035</t>
-  </si>
-  <si>
-    <t>0.9164,0.0008,0.1058,0.0012</t>
-  </si>
-  <si>
-    <t>0.8987,0.0015,0.1502,0.0008</t>
-  </si>
-  <si>
-    <t>0.9926,0.0006,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.9940,0.0034,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9922,0.0019,0.0019,0.0009</t>
-  </si>
-  <si>
-    <t>0.9966,0.0022,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9948,0.0049,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9939,0.0048,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0033,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9939,0.0038,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.0179,0.8144,0.2528,0.0138</t>
-  </si>
-  <si>
-    <t>0.0123,0.1369,0.9597,0.0017</t>
-  </si>
-  <si>
-    <t>0.0148,0.0195,0.9780,0.0012</t>
-  </si>
-  <si>
-    <t>0.3013,0.0673,0.5501,0.0013</t>
-  </si>
-  <si>
-    <t>0.0013,0.0007,0.9980,0.0003</t>
-  </si>
-  <si>
-    <t>0.4995,0.0120,0.3008,0.0941</t>
-  </si>
-  <si>
-    <t>0.0972,0.0221,0.8897,0.0188</t>
-  </si>
-  <si>
-    <t>0.4697,0.0709,0.4892,0.0273</t>
-  </si>
-  <si>
-    <t>0.9798,0.0013,0.0043,0.0068</t>
-  </si>
-  <si>
-    <t>0.0213,0.0388,0.0012,0.9848</t>
-  </si>
-  <si>
-    <t>0.0367,0.0019,0.0006,0.9873</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0049,0.0002,0.0001,0.9986</t>
-  </si>
-  <si>
-    <t>0.4791,0.0313,0.0166,0.6347</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9770,0.0062,0.0031,0.0044</t>
+  </si>
+  <si>
+    <t>0.0081,0.0001,0.0001,0.9978</t>
+  </si>
+  <si>
+    <t>0.9529,0.0004,0.0001,0.0603</t>
+  </si>
+  <si>
+    <t>0.1457,0.0012,0.0005,0.9593</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9697,0.0530,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0034,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9886,0.0026,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.2600,0.0071,0.8207,0.0053</t>
+  </si>
+  <si>
+    <t>0.4504,0.0019,0.7832,0.0001</t>
+  </si>
+  <si>
+    <t>0.0326,0.0076,0.9618,0.0048</t>
+  </si>
+  <si>
+    <t>0.9586,0.0240,0.0079,0.0020</t>
+  </si>
+  <si>
+    <t>0.0033,0.9951,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0058,0.9866,0.0024,0.0020</t>
+  </si>
+  <si>
+    <t>0.0109,0.9783,0.0060,0.0028</t>
+  </si>
+  <si>
+    <t>0.0690,0.9418,0.0054,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.9987,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9805,0.0007,0.0190,0.0002</t>
+  </si>
+  <si>
+    <t>0.6226,0.0023,0.5829,0.0014</t>
+  </si>
+  <si>
+    <t>0.0082,0.0019,0.9897,0.0012</t>
+  </si>
+  <si>
+    <t>0.6986,0.0030,0.4476,0.0006</t>
+  </si>
+  <si>
+    <t>0.0936,0.0080,0.9520,0.0003</t>
+  </si>
+  <si>
+    <t>0.0133,0.0022,0.9839,0.0054</t>
+  </si>
+  <si>
+    <t>0.0082,0.0005,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.1194,0.8383,0.0919,0.0316</t>
+  </si>
+  <si>
+    <t>0.7993,0.1067,0.1524,0.0047</t>
+  </si>
+  <si>
+    <t>0.0018,0.0419,0.9970,0.0012</t>
+  </si>
+  <si>
+    <t>0.0166,0.8964,0.1590,0.0003</t>
+  </si>
+  <si>
+    <t>0.7801,0.1331,0.1193,0.0278</t>
+  </si>
+  <si>
+    <t>0.5478,0.0739,0.3583,0.0071</t>
+  </si>
+  <si>
+    <t>0.4078,0.7334,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.0011,0.9902,0.4257,0.0011</t>
+  </si>
+  <si>
+    <t>0.0640,0.4993,0.1853,0.0236</t>
+  </si>
+  <si>
+    <t>0.0407,0.0047,0.9672,0.0009</t>
+  </si>
+  <si>
+    <t>0.1359,0.0048,0.8813,0.0044</t>
+  </si>
+  <si>
+    <t>0.0297,0.0054,0.9711,0.0042</t>
+  </si>
+  <si>
+    <t>0.0150,0.0660,0.9891,0.0002</t>
+  </si>
+  <si>
+    <t>0.0128,0.9781,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.0066,0.0201,0.9790,0.0193</t>
+  </si>
+  <si>
+    <t>0.0118,0.9283,0.0116,0.3614</t>
+  </si>
+  <si>
+    <t>0.0080,0.9726,0.0550,0.0379</t>
+  </si>
+  <si>
+    <t>0.0373,0.9289,0.0839,0.0029</t>
+  </si>
+  <si>
+    <t>0.0007,0.9975,0.0172,0.0003</t>
+  </si>
+  <si>
+    <t>0.0069,0.0420,0.9848,0.0017</t>
+  </si>
+  <si>
+    <t>0.0036,0.5191,0.9832,0.0003</t>
+  </si>
+  <si>
+    <t>0.1848,0.0336,0.7842,0.0186</t>
+  </si>
+  <si>
+    <t>0.0141,0.0008,0.9923,0.0005</t>
+  </si>
+  <si>
+    <t>0.0697,0.0104,0.9582,0.0005</t>
+  </si>
+  <si>
+    <t>0.0206,0.0644,0.9407,0.0013</t>
+  </si>
+  <si>
+    <t>0.9907,0.0168,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9902,0.0008,0.0027,0.0018</t>
+  </si>
+  <si>
+    <t>0.9919,0.0034,0.0016,0.0013</t>
+  </si>
+  <si>
+    <t>0.0036,0.0868,0.9932,0.0087</t>
+  </si>
+  <si>
+    <t>0.9966,0.0016,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9945,0.0028,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.0113,0.3459,0.9584,0.0012</t>
+  </si>
+  <si>
+    <t>0.0058,0.0123,0.9884,0.0017</t>
+  </si>
+  <si>
+    <t>0.0074,0.0145,0.9758,0.0042</t>
+  </si>
+  <si>
+    <t>0.0018,0.9150,0.9664,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0010,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0081,0.9866,0.0062,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.9927,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8463,0.0079,0.2115,0.0037</t>
+  </si>
+  <si>
+    <t>0.9117,0.0263,0.0581,0.0013</t>
+  </si>
+  <si>
+    <t>0.0136,0.1175,0.9712,0.0051</t>
+  </si>
+  <si>
+    <t>0.0049,0.9415,0.5192,0.0007</t>
+  </si>
+  <si>
+    <t>0.0077,0.9461,0.3668,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9987,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9874,0.7400,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.0003,0.0076,0.9961</t>
+  </si>
+  <si>
+    <t>0.0005,0.0010,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0042,0.0002,0.0006,0.9977</t>
+  </si>
+  <si>
+    <t>0.0020,0.0037,0.0005,0.9978</t>
+  </si>
+  <si>
+    <t>0.0091,0.0016,0.0041,0.9919</t>
+  </si>
+  <si>
+    <t>0.0040,0.0061,0.0004,0.9965</t>
+  </si>
+  <si>
+    <t>0.0030,0.9636,0.8123,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.9132,0.9895,0.0001</t>
+  </si>
+  <si>
+    <t>0.0087,0.8514,0.7459,0.0026</t>
+  </si>
+  <si>
+    <t>0.0055,0.7090,0.9452,0.0012</t>
+  </si>
+  <si>
+    <t>0.0015,0.9864,0.5837,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.9882,0.1902,0.0007</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9932,0.0093,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9869,0.0196,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9959,0.0014,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9976,0.0008,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9970,0.0016,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0042,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0263,0.0034,0.9875,0.0009</t>
+  </si>
+  <si>
+    <t>0.1194,0.0029,0.9319,0.0014</t>
+  </si>
+  <si>
+    <t>0.9685,0.0025,0.0104,0.0031</t>
+  </si>
+  <si>
+    <t>0.0144,0.0010,0.9894,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.9963,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0153,0.9813,0.0041,0.0007</t>
+  </si>
+  <si>
+    <t>0.0095,0.9885,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0268,0.9658,0.0189,0.0008</t>
+  </si>
+  <si>
+    <t>0.0039,0.9924,0.0031,0.0005</t>
+  </si>
+  <si>
+    <t>0.0020,0.9953,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.1195,0.9053,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.8440,0.0405,0.1127,0.0043</t>
+  </si>
+  <si>
+    <t>0.7606,0.0246,0.2594,0.0128</t>
+  </si>
+  <si>
+    <t>0.7422,0.0045,0.3707,0.0031</t>
+  </si>
+  <si>
+    <t>0.2289,0.0149,0.7884,0.0122</t>
+  </si>
+  <si>
+    <t>0.0157,0.0126,0.2238,0.9503</t>
+  </si>
+  <si>
+    <t>0.0490,0.9467,0.1240,0.0009</t>
+  </si>
+  <si>
+    <t>0.0106,0.9806,0.0267,0.0010</t>
+  </si>
+  <si>
+    <t>0.0013,0.9952,0.0096,0.0020</t>
+  </si>
+  <si>
+    <t>0.0036,0.9823,0.1340,0.0098</t>
+  </si>
+  <si>
+    <t>0.0220,0.9687,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.6756,0.4102,0.0152,0.0015</t>
+  </si>
+  <si>
+    <t>0.1756,0.8549,0.0068,0.0007</t>
+  </si>
+  <si>
+    <t>0.9959,0.0009,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0007,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9930,0.0020,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9969,0.0005,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0011,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.4618,0.9904,0.0004</t>
+  </si>
+  <si>
+    <t>0.0068,0.5679,0.9434,0.0005</t>
+  </si>
+  <si>
+    <t>0.0143,0.0068,0.9800,0.0009</t>
+  </si>
+  <si>
+    <t>0.0100,0.0055,0.9865,0.0007</t>
+  </si>
+  <si>
+    <t>0.9847,0.0037,0.0042,0.0006</t>
+  </si>
+  <si>
+    <t>0.9423,0.0035,0.0391,0.0037</t>
+  </si>
+  <si>
+    <t>0.4519,0.0006,0.6912,0.0029</t>
+  </si>
+  <si>
+    <t>0.7324,0.0740,0.2133,0.0247</t>
+  </si>
+  <si>
+    <t>0.0466,0.0005,0.0001,0.9901</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0060,0.0004,0.9992</t>
+  </si>
+  <si>
+    <t>0.0123,0.0001,0.0001,0.9970</t>
+  </si>
+  <si>
+    <t>0.0033,0.7651,0.9708,0.0011</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.2088,0.8244,0.0020,0.0078</t>
+  </si>
+  <si>
+    <t>0.9938,0.0014,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.4037,0.6331,0.0088,0.0051</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.7519,0.0301,0.0314,0.2500</t>
+  </si>
+  <si>
+    <t>0.9971,0.0008,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0182,0.2022,0.9020,0.1348</t>
+  </si>
+  <si>
+    <t>0.9635,0.0016,0.0018,0.0369</t>
+  </si>
+  <si>
+    <t>0.9780,0.0025,0.0125,0.0029</t>
+  </si>
+  <si>
+    <t>0.0963,0.8859,0.0245,0.0121</t>
+  </si>
+  <si>
+    <t>0.9970,0.0008,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9326,0.0542,0.0217,0.0046</t>
+  </si>
+  <si>
+    <t>0.5478,0.4729,0.0091,0.0063</t>
+  </si>
+  <si>
+    <t>0.8158,0.2113,0.0137,0.0027</t>
+  </si>
+  <si>
+    <t>0.9578,0.0206,0.0112,0.0022</t>
+  </si>
+  <si>
+    <t>0.9825,0.0105,0.0047,0.0028</t>
+  </si>
+  <si>
+    <t>0.9950,0.0036,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9971,0.0009,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9951,0.0026,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9962,0.0016,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9965,0.0012,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.5264,0.5157,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.1950,0.8582,0.0064,0.0003</t>
+  </si>
+  <si>
+    <t>0.9086,0.1411,0.0039,0.0007</t>
+  </si>
+  <si>
+    <t>0.1096,0.1415,0.8890,0.0045</t>
+  </si>
+  <si>
+    <t>0.9657,0.0573,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9849,0.0183,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9957,0.0013,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9896,0.0124,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.0160,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.9473,0.0861,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0111,0.0068,0.9861,0.0022</t>
+  </si>
+  <si>
+    <t>0.0028,0.0244,0.9922,0.0038</t>
+  </si>
+  <si>
+    <t>0.0830,0.0014,0.9694,0.0004</t>
+  </si>
+  <si>
+    <t>0.0080,0.0364,0.9859,0.0017</t>
+  </si>
+  <si>
+    <t>0.0077,0.0053,0.9890,0.0017</t>
+  </si>
+  <si>
+    <t>0.0981,0.0004,0.9607,0.0002</t>
+  </si>
+  <si>
+    <t>0.0080,0.0038,0.9894,0.0006</t>
+  </si>
+  <si>
+    <t>0.6445,0.0199,0.4234,0.0047</t>
+  </si>
+  <si>
+    <t>0.0878,0.0027,0.9441,0.0012</t>
+  </si>
+  <si>
+    <t>0.2577,0.3535,0.3079,0.0053</t>
+  </si>
+  <si>
+    <t>0.3214,0.0393,0.7035,0.0032</t>
+  </si>
+  <si>
+    <t>0.2772,0.1716,0.5650,0.0097</t>
+  </si>
+  <si>
+    <t>0.6256,0.0049,0.4876,0.0008</t>
+  </si>
+  <si>
+    <t>0.8307,0.0105,0.1581,0.0115</t>
+  </si>
+  <si>
+    <t>0.4507,0.0293,0.6548,0.0024</t>
+  </si>
+  <si>
+    <t>0.0720,0.9441,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0417,0.9553,0.0041,0.0019</t>
+  </si>
+  <si>
+    <t>0.9869,0.0102,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9021,0.1588,0.0045,0.0007</t>
+  </si>
+  <si>
+    <t>0.0655,0.9433,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9647,0.0231,0.0054,0.0003</t>
+  </si>
+  <si>
+    <t>0.9900,0.0002,0.0058,0.0002</t>
+  </si>
+  <si>
+    <t>0.9786,0.0013,0.0065,0.0024</t>
+  </si>
+  <si>
+    <t>0.8198,0.0128,0.2364,0.0034</t>
+  </si>
+  <si>
+    <t>0.9294,0.0036,0.0781,0.0006</t>
+  </si>
+  <si>
+    <t>0.0212,0.0074,0.9666,0.0179</t>
+  </si>
+  <si>
+    <t>0.2425,0.2224,0.6370,0.0206</t>
+  </si>
+  <si>
+    <t>0.0497,0.1379,0.8844,0.0062</t>
+  </si>
+  <si>
+    <t>0.5727,0.0051,0.5663,0.0020</t>
+  </si>
+  <si>
+    <t>0.0332,0.3967,0.9208,0.0019</t>
+  </si>
+  <si>
+    <t>0.9921,0.0048,0.0009,0.0018</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0016,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9966,0.0024,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0066,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9963,0.0024,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0009,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9959,0.0021,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.0126,0.1916,0.9735,0.0029</t>
+  </si>
+  <si>
+    <t>0.1118,0.1650,0.8135,0.0070</t>
+  </si>
+  <si>
+    <t>0.9053,0.0050,0.0592,0.0051</t>
+  </si>
+  <si>
+    <t>0.0046,0.0021,0.9944,0.0002</t>
+  </si>
+  <si>
+    <t>0.0067,0.0020,0.9896,0.0008</t>
+  </si>
+  <si>
+    <t>0.0226,0.0663,0.9405,0.0016</t>
+  </si>
+  <si>
+    <t>0.0015,0.0021,0.9974,0.0006</t>
+  </si>
+  <si>
+    <t>0.0085,0.0123,0.9824,0.0044</t>
+  </si>
+  <si>
+    <t>0.0006,0.0016,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0167,0.0030,0.9812,0.0014</t>
+  </si>
+  <si>
+    <t>0.0103,0.0129,0.9775,0.0162</t>
+  </si>
+  <si>
+    <t>0.6955,0.0306,0.3142,0.0136</t>
+  </si>
+  <si>
+    <t>0.7041,0.0008,0.4457,0.0009</t>
+  </si>
+  <si>
+    <t>0.9942,0.0004,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0015,0.0002,0.0024</t>
+  </si>
+  <si>
+    <t>0.9921,0.0073,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0022,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9948,0.0039,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.0478,0.0567,0.8785,0.0011</t>
+  </si>
+  <si>
+    <t>0.0057,0.0047,0.9925,0.0006</t>
+  </si>
+  <si>
+    <t>0.0347,0.0047,0.9648,0.0010</t>
+  </si>
+  <si>
+    <t>0.0409,0.0109,0.9535,0.0089</t>
+  </si>
+  <si>
+    <t>0.0031,0.0004,0.9967,0.0003</t>
+  </si>
+  <si>
+    <t>0.2129,0.0066,0.4276,0.2335</t>
+  </si>
+  <si>
+    <t>0.4293,0.0213,0.5788,0.0285</t>
+  </si>
+  <si>
+    <t>0.8182,0.0041,0.3145,0.0010</t>
+  </si>
+  <si>
+    <t>0.8352,0.0004,0.0005,0.3560</t>
+  </si>
+  <si>
+    <t>0.0859,0.0195,0.0018,0.9486</t>
+  </si>
+  <si>
+    <t>0.0347,0.0069,0.0005,0.9850</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.0011,0.0005,0.0002,0.9992</t>
+  </si>
+  <si>
+    <t>0.9228,0.0087,0.0028,0.0689</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1956,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1970,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1984,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +1998,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2057,7 +2054,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2068,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2082,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2110,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2124,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2138,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2152,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2166,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2180,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2194,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2208,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2222,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2236,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2250,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2264,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2275,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2292,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2303,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2320,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2334,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2348,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2359,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2376,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2390,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2404,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2418,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2432,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2446,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2471,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2488,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2502,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2516,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2530,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2544,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2569,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2586,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2600,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2614,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2628,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2639,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2656,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2684,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2698,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2726,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2740,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2768,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2782,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2796,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2807,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2824,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2838,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2852,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2866,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2880,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2894,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2905,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2919,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2936,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2950,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2961,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2978,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2989,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3006,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3020,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3034,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3048,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3062,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3076,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3090,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3104,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3115,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3132,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3146,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3157,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3314,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3328,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3356,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3370,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>325</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3566,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
         <v>380</v>
@@ -3692,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
         <v>389</v>
@@ -3706,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>390</v>
@@ -3779,7 +3776,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>358</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3790,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3818,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3829,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3843,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3860,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3874,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3888,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3902,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3916,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3927,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3944,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3958,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3972,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3986,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4000,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4028,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4053,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4070,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4112,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4126,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4154,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4193,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4280,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4294,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4308,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4322,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4336,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4347,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4361,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4378,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4392,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4406,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4420,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4434,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4448,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4462,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4476,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4490,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4504,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4532,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4546,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4560,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4574,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4585,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4602,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4613,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4630,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4644,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4655,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4672,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4686,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4700,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4714,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4728,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4742,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4756,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4770,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4784,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4798,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4812,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4823,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4840,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4854,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4868,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,10 +4879,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4896,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4910,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4938,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4952,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4966,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4980,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +4994,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5008,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5033,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5050,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5064,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5078,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5092,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5106,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5120,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5134,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5148,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5162,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5190,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5204,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5218,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5232,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5246,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5260,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5274,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5288,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5302,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5316,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,10 +5327,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5358,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5372,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5386,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5397,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5414,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5428,7 @@
         <v>259</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5442,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5456,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5470,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5484,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5498,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5509,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
